--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484331_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484331_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7257</v>
+        <v>2.0429</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2606</v>
+        <v>0.0022</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9863</v>
+        <v>2.0408</v>
       </c>
       <c r="G2" t="n">
         <v>1.7011</v>
@@ -610,13 +610,13 @@
         <v>2.1488</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.5264</v>
+        <v>-1.2092</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.6451</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6186</v>
+        <v>-0.5641</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5977</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0297</v>
+        <v>0.2349</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0279</v>
+        <v>0.0732</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0018</v>
+        <v>0.1616</v>
       </c>
       <c r="G3" t="n">
         <v>-2.535</v>
@@ -688,13 +688,13 @@
         <v>0.7814</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7796999999999999</v>
+        <v>-0.5152</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5447</v>
+        <v>-0.4436</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.235</v>
+        <v>-0.0716</v>
       </c>
       <c r="V3" t="n">
         <v>2.5037</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. PUERTAS GARCIA</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.3765</v>
+        <v>-1.4777</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0155</v>
+        <v>-0.9831</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3919</v>
+        <v>-0.4945</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.1171</v>
+        <v>-0.8636</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.7143</v>
+        <v>-1.7805</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.4029</v>
+        <v>0.9169</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.3388</v>
+        <v>-0.9041</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.2855</v>
+        <v>-0.8774999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0533</v>
+        <v>-0.0266</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7783</v>
+        <v>0.0405</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4287</v>
+        <v>-0.903</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3496</v>
+        <v>0.9435</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="S4" t="n">
-        <v>0.35</v>
+        <v>-0.5675</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2258</v>
+        <v>-0.079</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1242</v>
+        <v>-0.4885</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6093</v>
+        <v>-1.2186</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1052</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.4959</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>A. FERNANDEZ QUILEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.5732</v>
+        <v>-1.5907</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9425</v>
+        <v>-0.9767</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6307</v>
+        <v>-0.614</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8636</v>
+        <v>-0.8093</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.7805</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9169</v>
+        <v>-0.8093</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9041</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.8774999999999999</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0266</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0405</v>
+        <v>-0.8093</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.903</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9435</v>
+        <v>-0.8093</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1721</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.663</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0384</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6246</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ QUILEZ</t>
+          <t>A. PUERTAS GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.5907</v>
+        <v>-2.2162</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9767</v>
+        <v>-0.4702</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.614</v>
+        <v>-1.746</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8093</v>
+        <v>-3.1171</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-1.7143</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8093</v>
+        <v>-1.4029</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-1.3388</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-1.2855</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.0533</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8093</v>
+        <v>-1.7783</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.4287</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8093</v>
+        <v>-1.3496</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7814</v>
+        <v>0.7814</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1953</v>
+        <v>1.7581</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0.4897</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.2598</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.2299</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.1052</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.4244</v>
+        <v>-2.4474</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.5822</v>
+        <v>-2.36</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1577</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>-0.12</v>
@@ -1000,13 +1000,13 @@
         <v>2.7348</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1677</v>
+        <v>-1.1906</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3878</v>
+        <v>-0.1656</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7799</v>
+        <v>-1.025</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9414</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.3191</v>
+        <v>-2.9553</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.1296</v>
+        <v>-2.7657</v>
       </c>
       <c r="F8" t="n">
         <v>-0.1895</v>
@@ -1078,10 +1078,10 @@
         <v>2.3441</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.9067</v>
+        <v>-1.5428</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0894</v>
+        <v>-0.7255</v>
       </c>
       <c r="U8" t="n">
         <v>-0.8173</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. HERETER MARCHANTE</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7507</v>
+        <v>-3.1843</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9783</v>
+        <v>-1.8602</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7724</v>
+        <v>-1.324</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.2535</v>
+        <v>-3.5672</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6344</v>
+        <v>-1.3556</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.619</v>
+        <v>-2.2116</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2853</v>
+        <v>-1.3196</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2853</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.7274</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9682</v>
+        <v>-2.2476</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3492</v>
+        <v>-0.7634</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.619</v>
+        <v>-1.4842</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.1953</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.345</v>
+        <v>-0.7538</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0522</v>
+        <v>-0.1732</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2928</v>
+        <v>-0.5806</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1522</v>
+        <v>0.9414</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6642</v>
+        <v>0.6093</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.488</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>G. HERETER MARCHANTE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8671</v>
+        <v>-3.8651</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3252</v>
+        <v>-2.12</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5419</v>
+        <v>-1.7451</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.5672</v>
+        <v>-2.2535</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3556</v>
+        <v>-0.6344</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.2116</v>
+        <v>-1.619</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3196</v>
+        <v>-0.2853</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.2853</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7274</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.2476</v>
+        <v>-1.9682</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7634</v>
+        <v>-0.3492</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.4842</v>
+        <v>-1.619</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4367</v>
+        <v>-0.4595</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6382</v>
+        <v>-0.1939</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7985</v>
+        <v>-0.2656</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9414</v>
+        <v>-1.1522</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6093</v>
+        <v>-0.6642</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3321</v>
+        <v>-0.488</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.4489</v>
+        <v>-5.1885</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4824</v>
+        <v>-2.9768</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9665</v>
+        <v>-2.2116</v>
       </c>
       <c r="G11" t="n">
         <v>-2.9804</v>
@@ -1312,13 +1312,13 @@
         <v>1.7581</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1209</v>
+        <v>-0.8605</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8803</v>
+        <v>-0.3747</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2406</v>
+        <v>-0.4858</v>
       </c>
       <c r="V11" t="n">
         <v>-1.1522</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.5017</v>
+        <v>-5.9038</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.1081</v>
+        <v>-4.7553</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3936</v>
+        <v>-1.1485</v>
       </c>
       <c r="G12" t="n">
         <v>-2.5877</v>
@@ -1390,13 +1390,13 @@
         <v>2.5395</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7307</v>
+        <v>-1.1328</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3936</v>
+        <v>-0.2537</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.1243</v>
+        <v>-0.8791</v>
       </c>
       <c r="V12" t="n">
         <v>-2.7693</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-27.1563</v>
+        <v>-26.5512</v>
       </c>
       <c r="E13" t="n">
-        <v>-19.798</v>
+        <v>-19.1926</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.3583</v>
+        <v>-7.3582</v>
       </c>
       <c r="G13" t="n">
         <v>-17.6033</v>
@@ -1468,13 +1468,13 @@
         <v>17.581</v>
       </c>
       <c r="S13" t="n">
-        <v>-9.3268</v>
+        <v>-8.7216</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.9194</v>
+        <v>-3.3141</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.4074</v>
+        <v>-5.407500000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-3.1561</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.7917</v>
+        <v>9.079599999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>8.9842</v>
+        <v>6.3552</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8075</v>
+        <v>2.7244</v>
       </c>
       <c r="G14" t="n">
         <v>2.8245</v>
@@ -1546,13 +1546,13 @@
         <v>2.1488</v>
       </c>
       <c r="S14" t="n">
-        <v>4.4165</v>
+        <v>1.7044</v>
       </c>
       <c r="T14" t="n">
-        <v>3.9924</v>
+        <v>1.3634</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4241</v>
+        <v>0.341</v>
       </c>
       <c r="V14" t="n">
         <v>3.3787</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.295299999999999</v>
+        <v>6.9859</v>
       </c>
       <c r="E15" t="n">
-        <v>5.1436</v>
+        <v>3.728</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1517</v>
+        <v>3.2579</v>
       </c>
       <c r="G15" t="n">
         <v>4.5953</v>
@@ -1624,13 +1624,13 @@
         <v>1.7581</v>
       </c>
       <c r="S15" t="n">
-        <v>4.0208</v>
+        <v>2.7114</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1368</v>
+        <v>1.7211</v>
       </c>
       <c r="U15" t="n">
-        <v>0.884</v>
+        <v>0.9903</v>
       </c>
       <c r="V15" t="n">
         <v>1.8279</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.6806</v>
+        <v>5.369</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0554</v>
+        <v>2.6621</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6253</v>
+        <v>2.707</v>
       </c>
       <c r="G16" t="n">
         <v>3.3777</v>
@@ -1702,13 +1702,13 @@
         <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6267</v>
+        <v>1.3151</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0083</v>
+        <v>0.615</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>-0.8865</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.1135</v>
+        <v>4.2119</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9255</v>
+        <v>2.0266</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1881</v>
+        <v>2.1853</v>
       </c>
       <c r="G17" t="n">
         <v>3.95</v>
@@ -1780,13 +1780,13 @@
         <v>2.1488</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3123</v>
+        <v>1.4107</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5614</v>
+        <v>0.6625</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7509</v>
+        <v>0.7482</v>
       </c>
       <c r="V17" t="n">
         <v>0.6093</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.8873</v>
+        <v>2.79</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7173</v>
+        <v>-0.5151</v>
       </c>
       <c r="F18" t="n">
-        <v>3.6046</v>
+        <v>3.3051</v>
       </c>
       <c r="G18" t="n">
         <v>-0.3855</v>
@@ -1858,13 +1858,13 @@
         <v>0.9767</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3547</v>
+        <v>1.2573</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1899</v>
+        <v>0.3921</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1647</v>
+        <v>0.8652</v>
       </c>
       <c r="V18" t="n">
         <v>0.9414</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. PALLARES ARUMI</t>
+          <t>O. SUBIRANAS CASELLAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4333</v>
+        <v>2.577</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.0283</v>
       </c>
       <c r="F19" t="n">
-        <v>0.715</v>
+        <v>2.5487</v>
       </c>
       <c r="G19" t="n">
-        <v>2.0573</v>
+        <v>1.5434</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2768</v>
+        <v>1.382</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7805</v>
+        <v>0.1615</v>
       </c>
       <c r="J19" t="n">
-        <v>1.9976</v>
+        <v>0.2053</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0819</v>
+        <v>0.7176</v>
       </c>
       <c r="L19" t="n">
-        <v>1.9157</v>
+        <v>-0.5122</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0597</v>
+        <v>1.3381</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1949</v>
+        <v>0.6644</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1352</v>
+        <v>0.6737</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3907</v>
+        <v>1.3674</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2333</v>
+        <v>1.549</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3026</v>
+        <v>0.4871</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0693</v>
+        <v>1.0619</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.8828</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. SUBIRANAS CASELLAS</t>
+          <t>F. PALLARES ARUMI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.3636</v>
+        <v>1.8248</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1851</v>
+        <v>0.9205</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5487</v>
+        <v>0.9043</v>
       </c>
       <c r="G20" t="n">
-        <v>1.5434</v>
+        <v>2.0573</v>
       </c>
       <c r="H20" t="n">
-        <v>1.382</v>
+        <v>0.2768</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1615</v>
+        <v>1.7805</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2053</v>
+        <v>1.9976</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7176</v>
+        <v>0.0819</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5122</v>
+        <v>1.9157</v>
       </c>
       <c r="M20" t="n">
-        <v>1.3381</v>
+        <v>0.0597</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6644</v>
+        <v>0.1949</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6737</v>
+        <v>-0.1352</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3674</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3356</v>
+        <v>0.1582</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.1004</v>
       </c>
       <c r="U20" t="n">
-        <v>1.0619</v>
+        <v>0.2586</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.8828</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8228</v>
+        <v>-0.7753</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9989</v>
+        <v>-1.4933</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1761</v>
+        <v>0.7181</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1253</v>
@@ -2170,13 +2170,13 @@
         <v>1.3674</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1115</v>
+        <v>-0.064</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4842</v>
+        <v>0.0214</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6274</v>
+        <v>-0.0854</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9811</v>
+        <v>-1.0748</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1148</v>
+        <v>-1.5081</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1337</v>
+        <v>0.4333</v>
       </c>
       <c r="G23" t="n">
         <v>0.452</v>
@@ -2248,13 +2248,13 @@
         <v>1.1721</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4331</v>
+        <v>0.4732</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4237</v>
+        <v>0.183</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0094</v>
+        <v>0.2902</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2186</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2349</v>
+        <v>-2.1134</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.5567</v>
+        <v>-3.95</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3218</v>
+        <v>1.8365</v>
       </c>
       <c r="G24" t="n">
         <v>-0.9018</v>
@@ -2326,13 +2326,13 @@
         <v>1.1721</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9619</v>
+        <v>0.1596</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5447</v>
+        <v>0.062</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4172</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>0.3869</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>27.1562</v>
+        <v>28.5044</v>
       </c>
       <c r="E25" t="n">
-        <v>7.358300000000003</v>
+        <v>7.3584</v>
       </c>
       <c r="F25" t="n">
-        <v>19.79800000000001</v>
+        <v>21.1461</v>
       </c>
       <c r="G25" t="n">
         <v>17.6034</v>
@@ -2386,7 +2386,7 @@
         <v>4.0524</v>
       </c>
       <c r="M25" t="n">
-        <v>5.218999999999999</v>
+        <v>5.219</v>
       </c>
       <c r="N25" t="n">
         <v>1.852300000000001</v>
@@ -2404,13 +2404,13 @@
         <v>14.6508</v>
       </c>
       <c r="S25" t="n">
-        <v>9.326800000000002</v>
+        <v>10.6749</v>
       </c>
       <c r="T25" t="n">
-        <v>5.407299999999999</v>
+        <v>5.4072</v>
       </c>
       <c r="U25" t="n">
-        <v>3.9193</v>
+        <v>5.2677</v>
       </c>
       <c r="V25" t="n">
         <v>3.156300000000001</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484331_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484331_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -558,7 +563,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -626,1026 +631,1092 @@
       </c>
       <c r="X2" t="n">
         <v>0.0664</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484331_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. REGUANT MAJEM</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2349</v>
+        <v>0.607</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0732</v>
+        <v>0.607</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1616</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.535</v>
+        <v>0.607</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1215</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.6565</v>
+        <v>0.607</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.9204</v>
+        <v>0.607</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0614</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.9818</v>
+        <v>0.607</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6146</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0601</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6747</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5152</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4436</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0716</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>2.5037</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0664</v>
+        <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484331_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.4777</v>
+        <v>0.307</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9831</v>
+        <v>0.307</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4945</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8636</v>
+        <v>0.307</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.7805</v>
+        <v>0.307</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9169</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9041</v>
+        <v>0.307</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.8774999999999999</v>
+        <v>0.307</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0266</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0405</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.903</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9435</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5675</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.079</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4885</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484331_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ QUILEZ</t>
+          <t>P. REGUANT MAJEM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.5907</v>
+        <v>0.2349</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9767</v>
+        <v>0.0732</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.614</v>
+        <v>0.1616</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8093</v>
+        <v>-2.535</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.1215</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8093</v>
+        <v>-2.6565</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-1.9204</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.0614</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-1.9818</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8093</v>
+        <v>-0.6146</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.0601</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8093</v>
+        <v>-0.6747</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7814</v>
+        <v>0.7814</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0.5152</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0.4436</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.0716</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2.5037</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.0664</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484331_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. PUERTAS GARCIA</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.2162</v>
+        <v>-1.4777</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4702</v>
+        <v>-0.9831</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.746</v>
+        <v>-0.4945</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.1171</v>
+        <v>-0.8636</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7143</v>
+        <v>-1.7805</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.4029</v>
+        <v>0.9169</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.3388</v>
+        <v>-0.9041</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.2855</v>
+        <v>-0.8774999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0533</v>
+        <v>-0.0266</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7783</v>
+        <v>0.0405</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4287</v>
+        <v>-0.903</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3496</v>
+        <v>0.9435</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4897</v>
+        <v>-0.5675</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2598</v>
+        <v>-0.079</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2299</v>
+        <v>-0.4885</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6093</v>
+        <v>-1.2186</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1052</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4959</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484331_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>A. FERNANDEZ QUILEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.4474</v>
+        <v>-1.5907</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.36</v>
+        <v>-0.9767</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.614</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.12</v>
+        <v>-0.8093</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3093</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1893</v>
+        <v>-0.8093</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4585</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2126</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.754</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5785</v>
+        <v>-0.8093</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5219</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9433</v>
+        <v>-0.8093</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1953</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7348</v>
+        <v>0.1953</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1906</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1656</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.025</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484331_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>A. PUERTAS GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.9553</v>
+        <v>-2.2162</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7657</v>
+        <v>-0.4702</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1895</v>
+        <v>-1.746</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4706</v>
+        <v>-3.1171</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3492</v>
+        <v>-1.7143</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1214</v>
+        <v>-1.4029</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3122</v>
+        <v>-1.3388</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7585</v>
+        <v>-1.2855</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5537</v>
+        <v>-0.0533</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7828</v>
+        <v>-1.7783</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1077</v>
+        <v>-0.4287</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6751</v>
+        <v>-1.3496</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3441</v>
+        <v>1.7581</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5428</v>
+        <v>-0.4897</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7255</v>
+        <v>-0.2598</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8173</v>
+        <v>-0.2299</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6209</v>
+        <v>0.6093</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5545</v>
+        <v>2.1052</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0664</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484331_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>I. ISERN CASES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1843</v>
+        <v>-2.9553</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8602</v>
+        <v>-2.7657</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.324</v>
+        <v>-0.1895</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.5672</v>
+        <v>-0.4706</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3556</v>
+        <v>-0.3492</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.2116</v>
+        <v>-0.1214</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3196</v>
+        <v>1.3122</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5921999999999999</v>
+        <v>0.7585</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7274</v>
+        <v>0.5537</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.2476</v>
+        <v>-1.7828</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7634</v>
+        <v>-1.1077</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4842</v>
+        <v>-0.6751</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1953</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1721</v>
+        <v>2.3441</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7538</v>
+        <v>-1.5428</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1732</v>
+        <v>-0.7255</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5806</v>
+        <v>-0.8173</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9414</v>
+        <v>0.6209</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6093</v>
+        <v>0.5545</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3321</v>
+        <v>0.0664</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484331_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. HERETER MARCHANTE</t>
+          <t>P. CARRION SORIANO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8651</v>
+        <v>-3.0544</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.12</v>
+        <v>-2.967</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7451</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.2535</v>
+        <v>-0.727</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6344</v>
+        <v>-0.3093</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.619</v>
+        <v>-0.4177</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2853</v>
+        <v>-0.1485</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2853</v>
+        <v>1.2126</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-1.361</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9682</v>
+        <v>-0.5785</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3492</v>
+        <v>-1.5219</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.619</v>
+        <v>0.9433</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9767</v>
+        <v>2.7348</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4595</v>
+        <v>-1.1906</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1939</v>
+        <v>-0.1656</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2656</v>
+        <v>-1.025</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1522</v>
+        <v>-0.9414</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.488</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484331_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.1885</v>
+        <v>-3.1843</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9768</v>
+        <v>-1.8602</v>
       </c>
       <c r="F11" t="n">
+        <v>-1.324</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-3.5672</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-1.3556</v>
+      </c>
+      <c r="I11" t="n">
         <v>-2.2116</v>
       </c>
-      <c r="G11" t="n">
-        <v>-2.9804</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-2.6964</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-0.2841</v>
-      </c>
       <c r="J11" t="n">
-        <v>-0.6487000000000001</v>
+        <v>-1.3196</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7701</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1214</v>
+        <v>-0.7274</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.3318</v>
+        <v>-2.2476</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.9263</v>
+        <v>-0.7634</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4054</v>
+        <v>-1.4842</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1953</v>
+        <v>0.1953</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8605</v>
+        <v>-0.7538</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3747</v>
+        <v>-0.1732</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4858</v>
+        <v>-0.5806</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.1522</v>
+        <v>0.9414</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1522</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484331_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. VILAR FERNANDEZ</t>
+          <t>G. HERETER MARCHANTE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.9038</v>
+        <v>-3.8651</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.7553</v>
+        <v>-2.12</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1485</v>
+        <v>-1.7451</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.5877</v>
+        <v>-2.2535</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.8954</v>
+        <v>-0.6344</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3077</v>
+        <v>-1.619</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.8841</v>
+        <v>-0.2853</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.6529</v>
+        <v>-0.2853</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7688</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7036</v>
+        <v>-1.9682</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.2425</v>
+        <v>-0.3492</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5389</v>
+        <v>-1.619</v>
       </c>
       <c r="P12" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>2.5395</v>
+        <v>0.9767</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1328</v>
+        <v>-0.4595</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2537</v>
+        <v>-0.1939</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8791</v>
+        <v>-0.2656</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.7693</v>
+        <v>-1.1522</v>
       </c>
       <c r="W12" t="n">
         <v>-0.6642</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1052</v>
+        <v>-0.488</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484331_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. ABELLO GIRVES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-26.5512</v>
+        <v>-5.4955</v>
       </c>
       <c r="E13" t="n">
-        <v>-19.1926</v>
+        <v>-3.2838</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.3582</v>
+        <v>-2.2116</v>
       </c>
       <c r="G13" t="n">
-        <v>-17.6033</v>
+        <v>-3.2874</v>
       </c>
       <c r="H13" t="n">
-        <v>-10.1843</v>
+        <v>-3.0034</v>
       </c>
       <c r="I13" t="n">
-        <v>-7.419099999999998</v>
+        <v>-0.2841</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.218900000000001</v>
+        <v>-0.9557</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.8523</v>
+        <v>-1.0771</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.3665</v>
+        <v>0.1214</v>
       </c>
       <c r="M13" t="n">
-        <v>-12.3845</v>
+        <v>-2.3318</v>
       </c>
       <c r="N13" t="n">
-        <v>-8.331999999999999</v>
+        <v>-1.9263</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.0525</v>
+        <v>-0.4054</v>
       </c>
       <c r="P13" t="n">
-        <v>2.9303</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.6506</v>
+        <v>-1.9534</v>
       </c>
       <c r="R13" t="n">
-        <v>17.581</v>
+        <v>1.7581</v>
       </c>
       <c r="S13" t="n">
-        <v>-8.7216</v>
+        <v>-0.8605</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.3141</v>
+        <v>-0.3747</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.407500000000001</v>
+        <v>-0.4858</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.1561</v>
+        <v>-1.1522</v>
       </c>
       <c r="W13" t="n">
-        <v>3.9909</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.1472</v>
+        <v>-1.1522</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484331_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. VIDAL AGRA</t>
+          <t>F. VILAR FERNANDEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.079599999999999</v>
+        <v>-5.9038</v>
       </c>
       <c r="E14" t="n">
-        <v>6.3552</v>
+        <v>-4.7553</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7244</v>
+        <v>-1.1485</v>
       </c>
       <c r="G14" t="n">
-        <v>2.8245</v>
+        <v>-2.5877</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7345</v>
+        <v>-3.8954</v>
       </c>
       <c r="I14" t="n">
-        <v>2.09</v>
+        <v>1.3077</v>
       </c>
       <c r="J14" t="n">
-        <v>2.0354</v>
+        <v>-1.8841</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6191</v>
+        <v>-2.6529</v>
       </c>
       <c r="L14" t="n">
-        <v>1.4163</v>
+        <v>0.7688</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7891</v>
+        <v>-0.7036</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1154</v>
+        <v>-1.2425</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6737</v>
+        <v>0.5389</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1488</v>
+        <v>2.5395</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7044</v>
+        <v>-1.1328</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3634</v>
+        <v>-0.2537</v>
       </c>
       <c r="U14" t="n">
-        <v>0.341</v>
+        <v>-0.8791</v>
       </c>
       <c r="V14" t="n">
-        <v>3.3787</v>
+        <v>-2.7693</v>
       </c>
       <c r="W14" t="n">
-        <v>3.9331</v>
+        <v>-0.6642</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5545</v>
+        <v>-2.1052</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484331_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. SIMON</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.9859</v>
+        <v>-26.5512</v>
       </c>
       <c r="E15" t="n">
-        <v>3.728</v>
+        <v>-19.1926</v>
       </c>
       <c r="F15" t="n">
-        <v>3.2579</v>
+        <v>-7.3582</v>
       </c>
       <c r="G15" t="n">
-        <v>4.5953</v>
+        <v>-17.6033</v>
       </c>
       <c r="H15" t="n">
-        <v>4.393</v>
+        <v>-10.1843</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2023</v>
+        <v>-7.4191</v>
       </c>
       <c r="J15" t="n">
-        <v>4.0857</v>
+        <v>-5.218900000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>4.0176</v>
+        <v>-1.8523</v>
       </c>
       <c r="L15" t="n">
-        <v>0.06809999999999999</v>
+        <v>-3.3665</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5096000000000001</v>
+        <v>-12.3845</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3753</v>
+        <v>-8.331999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1342</v>
+        <v>-4.0525</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.1488</v>
+        <v>2.9303</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.9069</v>
+        <v>-14.6506</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7581</v>
+        <v>17.581</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7114</v>
+        <v>-8.7216</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7211</v>
+        <v>-3.3141</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9903</v>
+        <v>-5.407500000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>1.8279</v>
+        <v>-3.1561</v>
       </c>
       <c r="W15" t="n">
-        <v>1.8279</v>
+        <v>3.9909</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
-      </c>
+        <v>-7.1472</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. VIDAL TEIXIDOR</t>
+          <t>C. VIDAL AGRA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.369</v>
+        <v>9.079599999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6621</v>
+        <v>6.3552</v>
       </c>
       <c r="F16" t="n">
-        <v>2.707</v>
+        <v>2.7244</v>
       </c>
       <c r="G16" t="n">
-        <v>3.3777</v>
+        <v>2.8245</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4093</v>
+        <v>0.7345</v>
       </c>
       <c r="I16" t="n">
-        <v>2.9684</v>
+        <v>2.09</v>
       </c>
       <c r="J16" t="n">
-        <v>2.3791</v>
+        <v>2.0354</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0844</v>
+        <v>0.6191</v>
       </c>
       <c r="L16" t="n">
-        <v>2.2947</v>
+        <v>1.4163</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9986</v>
+        <v>0.7891</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3249</v>
+        <v>0.1154</v>
       </c>
       <c r="O16" t="n">
         <v>0.6737</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5627</v>
+        <v>2.1488</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3151</v>
+        <v>1.7044</v>
       </c>
       <c r="T16" t="n">
-        <v>0.615</v>
+        <v>1.3634</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7000999999999999</v>
+        <v>0.341</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.8865</v>
+        <v>3.3787</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3321</v>
+        <v>3.9331</v>
       </c>
       <c r="X16" t="n">
         <v>-0.5545</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484331_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. LAJAY BOBEPARI</t>
+          <t>A. SIMON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.2119</v>
+        <v>6.9859</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0266</v>
+        <v>3.728</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1853</v>
+        <v>3.2579</v>
       </c>
       <c r="G17" t="n">
-        <v>3.95</v>
+        <v>4.5953</v>
       </c>
       <c r="H17" t="n">
-        <v>3.3298</v>
+        <v>4.393</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6202</v>
+        <v>0.2023</v>
       </c>
       <c r="J17" t="n">
-        <v>3.1658</v>
+        <v>4.0857</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9496</v>
+        <v>4.0176</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2161</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7843</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3802</v>
+        <v>0.3753</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4041</v>
+        <v>0.1342</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.7581</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q17" t="n">
         <v>-3.9069</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1488</v>
+        <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4107</v>
+        <v>2.7114</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6625</v>
+        <v>1.7211</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7482</v>
+        <v>0.9903</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6093</v>
+        <v>1.8279</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1052</v>
+        <v>1.8279</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484331_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. CANAL FERRER</t>
+          <t>D. VIDAL TEIXIDOR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.79</v>
+        <v>5.369</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5151</v>
+        <v>2.6621</v>
       </c>
       <c r="F18" t="n">
-        <v>3.3051</v>
+        <v>2.707</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3855</v>
+        <v>3.3777</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2504</v>
+        <v>0.4093</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.135</v>
+        <v>2.9684</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1845</v>
+        <v>2.3791</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5104</v>
+        <v>0.0844</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6741</v>
+        <v>2.2947</v>
       </c>
       <c r="M18" t="n">
-        <v>0.799</v>
+        <v>0.9986</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2599</v>
+        <v>0.3249</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5391</v>
+        <v>0.6737</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2573</v>
+        <v>1.3151</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3921</v>
+        <v>0.615</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8652</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9414</v>
+        <v>-0.8865</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>-0.3321</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6642</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484331_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. SUBIRANAS CASELLAS</t>
+          <t>A. LAJAY BOBEPARI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.577</v>
+        <v>4.2119</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0283</v>
+        <v>2.0266</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5487</v>
+        <v>2.1853</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5434</v>
+        <v>3.95</v>
       </c>
       <c r="H19" t="n">
-        <v>1.382</v>
+        <v>3.3298</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1615</v>
+        <v>0.6202</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2053</v>
+        <v>3.1658</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7176</v>
+        <v>2.9496</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5122</v>
+        <v>0.2161</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3381</v>
+        <v>0.7843</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6644</v>
+        <v>0.3802</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6737</v>
+        <v>0.4041</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3674</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.9069</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3674</v>
+        <v>2.1488</v>
       </c>
       <c r="S19" t="n">
-        <v>1.549</v>
+        <v>1.4107</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4871</v>
+        <v>0.6625</v>
       </c>
       <c r="U19" t="n">
-        <v>1.0619</v>
+        <v>0.7482</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8828</v>
+        <v>0.6093</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6642</v>
+        <v>2.1052</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2186</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484331_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. PALLARES ARUMI</t>
+          <t>J. CANAL FERRER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.8248</v>
+        <v>2.79</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9205</v>
+        <v>-0.5151</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9043</v>
+        <v>3.3051</v>
       </c>
       <c r="G20" t="n">
-        <v>2.0573</v>
+        <v>-0.3855</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2768</v>
+        <v>-0.2504</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7805</v>
+        <v>-0.135</v>
       </c>
       <c r="J20" t="n">
-        <v>1.9976</v>
+        <v>-1.1845</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0819</v>
+        <v>-0.5104</v>
       </c>
       <c r="L20" t="n">
-        <v>1.9157</v>
+        <v>-0.6741</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0597</v>
+        <v>0.799</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1949</v>
+        <v>0.2599</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1352</v>
+        <v>0.5391</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1582</v>
+        <v>1.2573</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1004</v>
+        <v>0.3921</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2586</v>
+        <v>0.8652</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.9414</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484331_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. TARRES HERNANDEZ</t>
+          <t>O. SUBIRANAS CASELLAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3703</v>
+        <v>2.577</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8958</v>
+        <v>0.0283</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5255</v>
+        <v>2.5487</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2158</v>
+        <v>1.5434</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1.382</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2158</v>
+        <v>0.1615</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0809</v>
+        <v>0.2053</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.7176</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0809</v>
+        <v>-0.5122</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1348</v>
+        <v>1.3381</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>0.6644</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1348</v>
+        <v>0.6737</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3907</v>
+        <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.549</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>0.4871</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.0619</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.8828</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484331_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. DEL VAL GARCIA</t>
+          <t>F. PALLARES ARUMI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2226,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7753</v>
+        <v>1.8248</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4933</v>
+        <v>0.9205</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7181</v>
+        <v>0.9043</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1253</v>
+        <v>2.0573</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6969</v>
+        <v>0.2768</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8221000000000001</v>
+        <v>1.7805</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4387</v>
+        <v>1.9976</v>
       </c>
       <c r="K22" t="n">
-        <v>1.1256</v>
+        <v>0.0819</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6869</v>
+        <v>1.9157</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5639</v>
+        <v>0.0597</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4287</v>
+        <v>0.1949</v>
       </c>
       <c r="O22" t="n">
         <v>-0.1352</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.586</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.064</v>
+        <v>0.1582</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0214</v>
+        <v>-0.1004</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0854</v>
+        <v>0.2586</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2186,12 +2287,17 @@
       </c>
       <c r="X22" t="n">
         <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484331_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. CRUZ URBANEJA</t>
+          <t>G. TARRES HERNANDEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.0748</v>
+        <v>-0.3703</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5081</v>
+        <v>-0.8958</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4333</v>
+        <v>0.5255</v>
       </c>
       <c r="G23" t="n">
-        <v>0.452</v>
+        <v>0.2158</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1533</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6052</v>
+        <v>0.2158</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2623</v>
+        <v>0.0809</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.9389</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1.2011</v>
+        <v>0.0809</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1897</v>
+        <v>0.1348</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2144</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4041</v>
+        <v>0.1348</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.7814</v>
+        <v>-0.586</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4732</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0.183</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2902</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484331_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E. SIMS SERRA</t>
+          <t>N. DEL VAL GARCIA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.1134</v>
+        <v>-0.7753</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.95</v>
+        <v>-1.4933</v>
       </c>
       <c r="F24" t="n">
-        <v>1.8365</v>
+        <v>0.7181</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.9018</v>
+        <v>-0.1253</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3658</v>
+        <v>0.6969</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.2677</v>
+        <v>-0.8221000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.0818</v>
+        <v>0.4387</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1855</v>
+        <v>1.1256</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.2673</v>
+        <v>-0.6869</v>
       </c>
       <c r="M24" t="n">
-        <v>0.18</v>
+        <v>-0.5639</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1804</v>
+        <v>-0.4287</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0004</v>
+        <v>-0.1352</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.7581</v>
+        <v>-0.586</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1596</v>
+        <v>-0.064</v>
       </c>
       <c r="T24" t="n">
-        <v>0.062</v>
+        <v>0.0214</v>
       </c>
       <c r="U24" t="n">
-        <v>0.09760000000000001</v>
+        <v>-0.0854</v>
       </c>
       <c r="V24" t="n">
-        <v>0.3869</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0.3869</v>
+        <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484331_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,68 +2475,235 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
+        <v>-1.0748</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-1.5081</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.4333</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-1.1533</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.6052</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.2623</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.9389</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.2011</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.1897</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.2144</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.4041</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.7814</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.4732</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.2902</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484331_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>E. SIMS SERRA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-2.1134</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-3.95</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.8365</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.9018</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.3658</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-1.2677</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-1.0818</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.1855</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-1.2673</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.1804</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-1.7581</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.1596</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.09760000000000001</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484331_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
         <v>28.5044</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E27" t="n">
         <v>7.3584</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F27" t="n">
         <v>21.1461</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G27" t="n">
         <v>17.6034</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H27" t="n">
         <v>10.1844</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I27" t="n">
         <v>7.419100000000002</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J27" t="n">
         <v>12.3845</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K27" t="n">
         <v>8.331999999999999</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L27" t="n">
         <v>4.0524</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M27" t="n">
         <v>5.219</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N27" t="n">
         <v>1.852300000000001</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O27" t="n">
         <v>3.3666</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P27" t="n">
         <v>-2.9302</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q27" t="n">
         <v>-17.5808</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R27" t="n">
         <v>14.6508</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S27" t="n">
         <v>10.6749</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T27" t="n">
         <v>5.4072</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U27" t="n">
         <v>5.2677</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V27" t="n">
         <v>3.156300000000001</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W27" t="n">
         <v>7.1471</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X27" t="n">
         <v>-3.991</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
